--- a/AvrNetIO-Anschluesse.xlsx
+++ b/AvrNetIO-Anschluesse.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daten\AvrProgs\i-Telex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A535C6CC-26FA-4DFD-92FA-FC04089D4205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD679CD-EBB4-4D59-B054-42F568BC6D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="-555" windowWidth="29040" windowHeight="15990" xr2:uid="{DAF96758-D4CB-483D-B41C-05E3EF715EF6}"/>
+    <workbookView xWindow="25080" yWindow="-645" windowWidth="29040" windowHeight="15840" xr2:uid="{DAF96758-D4CB-483D-B41C-05E3EF715EF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="64">
   <si>
     <t>ATmegaXX4</t>
   </si>
@@ -46,9 +45,6 @@
     <t>Funktion</t>
   </si>
   <si>
-    <t>iTelex Bus</t>
-  </si>
-  <si>
     <t>VCC</t>
   </si>
   <si>
@@ -160,9 +156,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>auch ISP</t>
-  </si>
-  <si>
     <t>RTS</t>
   </si>
   <si>
@@ -179,6 +172,60 @@
   </si>
   <si>
     <t>A1</t>
+  </si>
+  <si>
+    <t>MOSI2</t>
+  </si>
+  <si>
+    <t>MISO2</t>
+  </si>
+  <si>
+    <t>CLK2</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>für Programmierausgang</t>
+  </si>
+  <si>
+    <t>ExtReset</t>
+  </si>
+  <si>
+    <t>eigentlich unbenutzt</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>an ENC, auch ISP input</t>
+  </si>
+  <si>
+    <t>an ENC</t>
+  </si>
+  <si>
+    <t>EXT</t>
+  </si>
+  <si>
+    <t>Bemerkung</t>
+  </si>
+  <si>
+    <t>iTelex Bus A4 C4</t>
+  </si>
+  <si>
+    <t>iTelex Bus A8 C8</t>
+  </si>
+  <si>
+    <t>iTelex Bus A6 C6</t>
+  </si>
+  <si>
+    <t>iTelex Bus A2 C2</t>
   </si>
 </sst>
 </file>
@@ -214,13 +261,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -536,10 +589,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC9F4DD3-DB12-41F2-A287-6D6B18027906}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -547,317 +603,476 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1">
         <v>15</v>
       </c>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" s="1">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2">
+        <v>9</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1">
         <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
       </c>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1">
         <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
       </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
         <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1">
         <v>6</v>
       </c>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1">
         <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1">
         <v>7</v>
       </c>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1">
         <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1">
         <v>8</v>
       </c>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1">
         <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1">
         <v>9</v>
       </c>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1">
         <v>40</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1">
         <v>10</v>
       </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11" s="1">
         <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1">
         <v>38</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1">
         <v>12</v>
       </c>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1">
         <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1">
         <v>13</v>
       </c>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1">
         <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1">
         <v>15</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="1">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="1">
+        <v>21</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="1">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>26</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="1">
-        <v>16</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="1">
-        <v>17</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>27</v>
       </c>
       <c r="B18" s="1">
         <v>6</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1">
         <v>7</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="1">
         <v>8</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1">
         <v>5</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="1">
+        <v>16</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="1">
+        <v>18</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="1">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="1">
+        <v>19</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="1">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="1">
+        <v>17</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/AvrNetIO-Anschluesse.xlsx
+++ b/AvrNetIO-Anschluesse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daten\AvrProgs\i-Telex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD679CD-EBB4-4D59-B054-42F568BC6D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8338379-A391-4DE8-B0BC-1EB2D5EFFF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25080" yWindow="-645" windowWidth="29040" windowHeight="15840" xr2:uid="{DAF96758-D4CB-483D-B41C-05E3EF715EF6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="84">
   <si>
     <t>ATmegaXX4</t>
   </si>
@@ -204,12 +204,6 @@
     <t>D7</t>
   </si>
   <si>
-    <t>an ENC, auch ISP input</t>
-  </si>
-  <si>
-    <t>an ENC</t>
-  </si>
-  <si>
     <t>EXT</t>
   </si>
   <si>
@@ -226,6 +220,72 @@
   </si>
   <si>
     <t>iTelex Bus A2 C2</t>
+  </si>
+  <si>
+    <t>INT(ENC)</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>an ENC 7, auch ISP input</t>
+  </si>
+  <si>
+    <t>an ENC 6, auch ISP input</t>
+  </si>
+  <si>
+    <t>an ENC 8, auch ISP input</t>
+  </si>
+  <si>
+    <t>an ENC 9</t>
+  </si>
+  <si>
+    <t>an ENC 4</t>
+  </si>
+  <si>
+    <t>ATmega2561</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>PIN SV4</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>F7</t>
+  </si>
+  <si>
+    <t>F6</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
+    <t>TCK</t>
+  </si>
+  <si>
+    <t>TDI</t>
+  </si>
+  <si>
+    <t>TDO</t>
+  </si>
+  <si>
+    <t>TMS</t>
+  </si>
+  <si>
+    <t>ISP 10pol</t>
+  </si>
+  <si>
+    <t>ISP Signal</t>
+  </si>
+  <si>
+    <t>SCK</t>
+  </si>
+  <si>
+    <t>RST</t>
   </si>
 </sst>
 </file>
@@ -261,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -274,6 +334,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -589,10 +652,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC9F4DD3-DB12-41F2-A287-6D6B18027906}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -609,10 +673,10 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -632,7 +696,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -652,7 +716,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -672,7 +736,7 @@
         <v>39</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -692,7 +756,7 @@
         <v>39</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -894,7 +958,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -914,7 +978,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -931,10 +995,10 @@
         <v>39</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -951,10 +1015,10 @@
         <v>39</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -971,10 +1035,10 @@
         <v>39</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -991,87 +1055,186 @@
         <v>39</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="1">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B23" s="1">
         <v>16</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="1">
+      <c r="D23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="1">
         <v>1</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="1">
-        <v>18</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="1">
-        <v>3</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H23" s="5"/>
+      <c r="I23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K23" s="5">
+        <v>1</v>
+      </c>
+      <c r="L23" s="5">
+        <v>1</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E24" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H24" s="5"/>
+      <c r="I24" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K24" s="5">
+        <v>9</v>
+      </c>
+      <c r="L24" s="5">
+        <v>9</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B25" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E25" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>51</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" s="5">
+        <v>3</v>
+      </c>
+      <c r="L25" s="5">
+        <v>7</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="1">
+        <v>17</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K26" s="5">
+        <v>5</v>
+      </c>
+      <c r="L26" s="5">
+        <v>5</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
